--- a/Input/TissueComposition.xlsx
+++ b/Input/TissueComposition.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wageningenur4.sharepoint.com/sites/PARCProjectChrysanthi-CChannel/Gedeelde documenten/C_Channel/CP_L_R/PARC_PFAS_PBPKmodel/Codes_PFAS_models/Chrysanthi_Pachoulide_2024_PFOA_mechanistic/Input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wageningenur4.sharepoint.com/sites/PARCProjectChrysanthi-CChannel/Gedeelde documenten/C_Channel/CP_L_R/PARC_PFOA_mechanistic/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:40009_{35847771-DD5A-4E90-B5B8-5F4FC973C904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27CD4C8B-3FBF-4C82-849A-440967E4989B}"/>
@@ -148,7 +148,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -630,7 +630,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1889,25 +1889,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="568ff3df-f16a-482d-bb3c-58af1efa1658">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002AA8BEAC825CAE4DA772B4C276EF423C" ma:contentTypeVersion="12" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="4363adfface29496c4692934bfc386e4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="568ff3df-f16a-482d-bb3c-58af1efa1658" xmlns:ns3="13cea704-446d-46be-be94-9e10425fef80" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5ef7a87983d964890dd86635184f037c" ns2:_="" ns3:_="">
     <xsd:import namespace="568ff3df-f16a-482d-bb3c-58af1efa1658"/>
@@ -2118,25 +2099,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557F1F23-71BD-4DD4-A92C-14574712ADD5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="568ff3df-f16a-482d-bb3c-58af1efa1658"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A56B336A-CA46-49EA-8652-4A4AAAF9C7BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="568ff3df-f16a-482d-bb3c-58af1efa1658">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5AFB47E-15C1-4E80-AF56-938B4A83CD9C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2153,4 +2135,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A56B336A-CA46-49EA-8652-4A4AAAF9C7BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557F1F23-71BD-4DD4-A92C-14574712ADD5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="568ff3df-f16a-482d-bb3c-58af1efa1658"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Input/TissueComposition.xlsx
+++ b/Input/TissueComposition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wageningenur4.sharepoint.com/sites/PARCProjectChrysanthi-CChannel/Gedeelde documenten/C_Channel/CP_L_R/PARC_PFOA_mechanistic/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:40009_{35847771-DD5A-4E90-B5B8-5F4FC973C904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27CD4C8B-3FBF-4C82-849A-440967E4989B}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:40009_{35847771-DD5A-4E90-B5B8-5F4FC973C904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5AFF555-7CDA-4861-81F8-02961BD605FF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33390" yWindow="2235" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TissueComposition" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="38">
   <si>
     <t>Tissue</t>
   </si>
@@ -101,21 +101,9 @@
     <t>Bone</t>
   </si>
   <si>
-    <t>assuming 0 for f_ALB but I'm not sure</t>
-  </si>
-  <si>
-    <t>storage lipids are total fat - total phospholipids (neutral + acidic)</t>
-  </si>
-  <si>
     <t>membrane lipids is neutral phospholipids</t>
   </si>
   <si>
-    <t>albimin in interstitial space</t>
-  </si>
-  <si>
-    <t>these values were slighly different in Utsey</t>
-  </si>
-  <si>
     <t>NamingInUtsey</t>
   </si>
   <si>
@@ -141,6 +129,24 @@
   </si>
   <si>
     <t>Rat</t>
+  </si>
+  <si>
+    <t>albumin in interstitial space</t>
+  </si>
+  <si>
+    <t>Stomach</t>
+  </si>
+  <si>
+    <t>Intestine</t>
+  </si>
+  <si>
+    <t>storage lipids are total fat minus total phospholipids (neutral + acidic)</t>
+  </si>
+  <si>
+    <t>assuming 0 for f_ALB</t>
+  </si>
+  <si>
+    <t>assuming the same as intestine as done in pksim (available data under: tissue_comp_R&amp;R_for_pksim.csv)</t>
   </si>
 </sst>
 </file>
@@ -627,10 +633,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -690,9 +697,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -730,7 +737,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -836,7 +843,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -978,7 +985,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -986,901 +993,941 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="59.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" style="2"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="G3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.153</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5.5300000000000002E-2</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.77100000000000002</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="3">
+        <v>4.7E-2</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1.26E-2</v>
+      </c>
+      <c r="D6" s="3">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="B7" s="3">
+        <v>4.7E-2</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.26E-2</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="C8" s="3">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="D8" s="3">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1.66E-2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1.4E-3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3.3E-3</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="3">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1.15E-2</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.1769</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="G10" s="3">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C11" s="3">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.79600000000000004</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="C12" s="3">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="D12" s="3">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.77300000000000002</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="3">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="C13" s="3">
+        <v>5.0200000000000002E-2</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1.8E-3</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1.4E-2</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1.03E-2</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.16239999999999999</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.80700000000000005</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C16" s="3">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.92800000000000005</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="3">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="D19" s="3">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.79800000000000004</v>
-      </c>
-      <c r="C4" s="2">
-        <v>4.7800000000000002E-2</v>
-      </c>
-      <c r="D4" s="2">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="3">
+        <v>3.1200000000000002E-2</v>
+      </c>
+      <c r="C20" s="3">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="3">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1.26E-2</v>
+      </c>
+      <c r="D21" s="3">
+        <v>7.000000000000001E-4</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5.6299999999999996E-2</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1.3999999999999999E-2</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1.06E-2</v>
+      </c>
+      <c r="D22" s="3">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="E4" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.153</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="C5" s="2">
-        <v>5.5300000000000002E-2</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.77100000000000002</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2">
-        <v>4.7E-2</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1.26E-2</v>
-      </c>
-      <c r="D6" s="2">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.79</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2">
-        <v>8.8999999999999996E-2</v>
-      </c>
-      <c r="C7" s="2">
-        <v>7.9000000000000008E-3</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="E22" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.73</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1.2E-2</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2.4E-2</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1.4000000000000002E-3</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.1769</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0.71700000000000008</v>
+      </c>
+      <c r="G23" s="3">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1.3999999999999999E-2</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2.3799999999999998E-2</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0.20749999999999999</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="G24" s="3">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="3">
+        <v>2.2000000000000002E-2</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1.23E-2</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0.53</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="C26" s="3">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="D26" s="3">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="E7" s="2">
-        <v>0.17</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.74199999999999999</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1.66E-2</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1.4E-3</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.16669999999999999</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.77800000000000002</v>
-      </c>
-      <c r="G8" s="2">
-        <v>3.3E-3</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1.15E-2</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.1769</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.73699999999999999</v>
-      </c>
-      <c r="G9" s="2">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="C10" s="2">
-        <v>5.5999999999999999E-3</v>
-      </c>
-      <c r="D10" s="2">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.18</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.79600000000000004</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="2">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>9.1999999999999998E-3</v>
-      </c>
-      <c r="D11" s="2">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.17</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.77300000000000002</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="E26" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="2">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="C12" s="2">
-        <v>5.0200000000000002E-2</v>
-      </c>
-      <c r="D12" s="2">
+      <c r="B27" s="3">
+        <v>2.4E-2</v>
+      </c>
+      <c r="C27" s="3">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="D27" s="3">
         <v>1.8E-3</v>
       </c>
-      <c r="E12" s="2">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="E27" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="2">
-        <v>1.4E-2</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1.03E-2</v>
-      </c>
-      <c r="D13" s="2">
+      <c r="B28" s="3">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1.0700000000000001E-2</v>
+      </c>
+      <c r="D28" s="3">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="E13" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0.78300000000000003</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="E28" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3.8999999999999998E-3</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1.7600000000000001E-2</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.16239999999999999</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0.80700000000000005</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="B29" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1.43E-2</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0.16570000000000001</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="C15" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="D15" s="2">
-        <v>2.9399999999999999E-2</v>
-      </c>
-      <c r="E15" s="2">
-        <v>2.2100000000000002E-2</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.92800000000000005</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="B30" s="3">
+        <v>2E-3</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="D30" s="3">
+        <v>2.4500000000000001E-2</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0.96</v>
+      </c>
+      <c r="G30" s="3">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1.0699999999999999E-2</v>
-      </c>
-      <c r="D16" s="2">
+      <c r="B31" s="3">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1.0700000000000001E-2</v>
+      </c>
+      <c r="D31" s="3">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E31" s="3">
         <v>0.12</v>
       </c>
-      <c r="F16" s="2">
-        <v>0.81</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="F31" s="3">
+        <v>0.86</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="2">
-        <v>7.3999999999999996E-2</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0.26800000000000002</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0.44600000000000001</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="2">
-        <v>0.85299999999999998</v>
-      </c>
-      <c r="C18" s="2">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="D18" s="2">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0.06</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="2">
-        <v>3.1200000000000002E-2</v>
-      </c>
-      <c r="C19" s="2">
-        <v>3.9399999999999998E-2</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0.77400000000000002</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="2">
-        <v>3.7999999999999999E-2</v>
-      </c>
-      <c r="C20" s="2">
-        <v>1.26E-2</v>
-      </c>
-      <c r="D20" s="2">
-        <v>7.000000000000001E-4</v>
-      </c>
-      <c r="E20" s="2">
-        <v>5.6299999999999996E-2</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0.76</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="2">
-        <v>1.3999999999999999E-2</v>
-      </c>
-      <c r="C21" s="2">
-        <v>1.06E-2</v>
-      </c>
-      <c r="D21" s="2">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0.73</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="2">
-        <v>1.2E-2</v>
-      </c>
-      <c r="C22" s="2">
-        <v>2.4E-2</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1.4000000000000002E-3</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0.1769</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0.71700000000000008</v>
-      </c>
-      <c r="G22" s="2">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="2">
-        <v>1.3999999999999999E-2</v>
-      </c>
-      <c r="C23" s="2">
-        <v>2.3799999999999998E-2</v>
-      </c>
-      <c r="D23" s="2">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0.20749999999999999</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0.58299999999999996</v>
-      </c>
-      <c r="G23" s="2">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="2">
-        <v>2.2000000000000002E-2</v>
-      </c>
-      <c r="C24" s="2">
-        <v>1.23E-2</v>
-      </c>
-      <c r="D24" s="2">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="E24" s="2">
-        <v>0.11</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0.53</v>
-      </c>
-      <c r="G24" s="2">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="C25" s="2">
-        <v>7.1999999999999998E-3</v>
-      </c>
-      <c r="D25" s="2">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E25" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="G25" s="2">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="2">
-        <v>2.4E-2</v>
-      </c>
-      <c r="C26" s="2">
-        <v>4.4000000000000003E-3</v>
-      </c>
-      <c r="D26" s="2">
-        <v>1.8E-3</v>
-      </c>
-      <c r="E26" s="2">
-        <v>0.41</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0.64500000000000002</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="C27" s="2">
-        <v>1.0700000000000001E-2</v>
-      </c>
-      <c r="D27" s="2">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0.52</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="C28" s="2">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="D28" s="2">
-        <v>1.43E-2</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0.16570000000000001</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0.82299999999999995</v>
-      </c>
-      <c r="G28" s="2">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>19</v>
-      </c>
-      <c r="B29" s="2">
-        <v>2E-3</v>
-      </c>
-      <c r="C29" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="D29" s="2">
-        <v>2.4500000000000001E-2</v>
-      </c>
-      <c r="E29" s="2">
-        <v>1.0200000000000001E-2</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0.96</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" s="2">
-        <v>0</v>
-      </c>
-      <c r="C30" s="2">
-        <v>1.0700000000000001E-2</v>
-      </c>
-      <c r="D30" s="2">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0.86</v>
-      </c>
-      <c r="G30" s="2">
-        <v>0</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B31" s="2">
+      <c r="B32" s="3">
         <v>7.3999999999999999E-4</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C32" s="3">
         <v>1.5999999999999999E-5</v>
       </c>
-      <c r="D31" s="2">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2">
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>2.6800000000000001E-3</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F32" s="3">
         <v>4.4600000000000004E-3</v>
       </c>
-      <c r="G31" s="2">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>35</v>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1889,6 +1936,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="568ff3df-f16a-482d-bb3c-58af1efa1658">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002AA8BEAC825CAE4DA772B4C276EF423C" ma:contentTypeVersion="12" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="4363adfface29496c4692934bfc386e4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="568ff3df-f16a-482d-bb3c-58af1efa1658" xmlns:ns3="13cea704-446d-46be-be94-9e10425fef80" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5ef7a87983d964890dd86635184f037c" ns2:_="" ns3:_="">
     <xsd:import namespace="568ff3df-f16a-482d-bb3c-58af1efa1658"/>
@@ -2099,26 +2165,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A56B336A-CA46-49EA-8652-4A4AAAF9C7BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="568ff3df-f16a-482d-bb3c-58af1efa1658">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557F1F23-71BD-4DD4-A92C-14574712ADD5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="568ff3df-f16a-482d-bb3c-58af1efa1658"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5AFB47E-15C1-4E80-AF56-938B4A83CD9C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2135,22 +2200,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A56B336A-CA46-49EA-8652-4A4AAAF9C7BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557F1F23-71BD-4DD4-A92C-14574712ADD5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="568ff3df-f16a-482d-bb3c-58af1efa1658"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>